--- a/www/download/IND.gross_output.s.du.rpO2.xlsx
+++ b/www/download/IND.gross_output.s.du.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>146610.289414564</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159526.213482853</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123979.695883322</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120450.347390909</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185742.496535168</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186186.938233551</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174513.130482041</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190918.985280122</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227249.957496472</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322455.394678893</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367044.227854961</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>384562.520861652</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>474700.695051238</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509090.748452466</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>463871.357345773</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70047.454523996</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79663.7534526347</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49912.3959232774</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57429.1776440292</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76672.2971034209</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89710.0377140288</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102971.707553904</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107043.547252388</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112006.151290124</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126413.966296076</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143259.790155488</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186559.188995831</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210129.287937022</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223464.259966833</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154034.08405748</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121436.343833867</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112863.069983447</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87903.3448988941</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92849.2989726976</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114157.875687926</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140302.439395547</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136065.511089189</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139297.248504199</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166008.824561457</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198888.637080127</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240063.02607829</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>269767.41733582</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>307728.194870485</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338516.342278976</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241836.914905597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18227.2130520174</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19514.848489872</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14772.812345833</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13206.0249433025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13276.0982277425</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12757.4842668453</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15626.7460869806</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18273.8949340895</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23122.5727474749</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31763.8357114598</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34665.2485700801</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46692.8511142255</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59785.2240842123</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66878.0084838731</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53281.1379701971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467663.702988195</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>488677.629836954</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448931.64894247</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437189.110483749</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>439184.529838364</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>481543.29565864</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470355.335969799</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>460494.763083101</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485483.620634169</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>620729.228483145</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>632569.915853734</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>706222.387070263</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>935792.28413597</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>1163648.24798007</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>946617.365827791</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189479.6829244</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>203223.446463751</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170684.16555648</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179463.392047268</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237961.802881988</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>317178.614684762</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339034.833538994</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277727.456179654</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300271.728450562</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391053.9194291</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>457214.977786973</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>519953.458312772</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>555766.829031762</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569009.775566893</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>443385.831777938</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.309</t>
+          <t>6309425.80972912</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.703</t>
+          <t>6702924.98705902</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5970308.79216022</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5.534</t>
+          <t>5534029.84041488</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.851</t>
+          <t>4850737.43963178</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.534</t>
+          <t>4534023.63689136</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.891</t>
+          <t>4890606.16342778</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.573</t>
+          <t>5572646.5852621</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6.864</t>
+          <t>6863865.53387348</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8.685</t>
+          <t>8684601.77024386</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.706</t>
+          <t>9705874.32959541</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.081</t>
+          <t>11081459.4582406</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>14.511</t>
+          <t>14511366.7679889</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17.154</t>
+          <t>17153993.8963372</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>17.786</t>
+          <t>17785982.5126019</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3946.86659694882</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4989.32029963541</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2886.31325347415</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3346.66819112788</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5208.60422856479</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5490.0921481529</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6518.93423053325</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7638.34525051202</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9244.85571875276</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9206.46299684954</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6229.86899247028</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6673.13822763928</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7419.66249719273</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9248.7457375628</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6066.85758162724</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33841.3220790746</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44442.0869687412</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28531.8739235183</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38318.9204768538</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47141.7115564076</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53269.9970912745</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67105.1602546248</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77346.3586074602</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86088.1877159198</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92703.6394794377</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107169.243944624</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123827.759401158</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135949.139327278</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145015.120762569</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86080.9665519187</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690246.863070835</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>653575.278340293</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505361.104424863</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>611732.57973023</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765344.753876624</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>880811.816571862</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>928748.616373829</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>934418.189717</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1041470.30920824</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1170227.73072777</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1236036.31248347</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1457837.7073856</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1610716.61233789</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1574917.12718363</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998773.182250808</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55976.2296051148</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59993.8561856547</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47309.7113251972</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55227.220322733</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53822.1981542492</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59003.3162240211</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63852.2950975562</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62227.6983532212</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74892.3494181828</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88874.1924953837</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101207.617524437</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107120.637245367</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121845.577157707</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129039.401024326</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89763.9215323537</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221970.003770939</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235075.940198637</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197370.7657054</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206944.408329211</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>284144.045778814</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403501.122299265</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>409770.796676972</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>421354.100403359</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491376.069813715</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>621891.981406997</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>774331.899340464</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>927021.20488757</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955871.320132572</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1062113.92808241</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>724166.47783921</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6249.21991067996</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6239.75514281726</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8771.09254223824</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9755.68878095268</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3919.45194936824</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11760.1141861366</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14066.2772846945</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14672.9940455874</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18261.5843430678</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12930.6028431197</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10606.8675474572</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11715.6066146397</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14529.4908698554</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15559.8458584383</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8776.69886600199</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50894.1732185413</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48067.2341106195</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34235.3306676527</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39411.4904559264</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50602.1034595017</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60523.5886455758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59521.3526260103</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58578.7073191823</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70749.9424325823</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82939.3739149149</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84503.6712227412</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105381.958614802</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114330.5253951</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115360.473828367</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65834.7467554089</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>464796.417569795</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>446693.800695532</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331361.661080739</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387894.345467806</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514415.060296161</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>638396.087059673</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>610597.43367641</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>617170.67037631</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>711779.306267404</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816263.187710282</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1005593.55963613</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>1129359.31392268</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.161</t>
+          <t>1161461.86169466</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1259529.23135778</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827029.472075952</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482041.026900044</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>493842.877302503</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384486.621986489</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405768.451747685</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477793.406049253</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>513833.087163428</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>467466.65816885</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456866.474748767</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>519109.42844331</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>629355.866274217</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758747.803538969</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>861584.952199877</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>949375.90122058</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>868573.245005548</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615039.927667925</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41436.3928747192</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50751.9835473069</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41701.6927553032</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42941.843548381</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49299.7098549978</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85972.9200288687</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75452.9849031966</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70583.4092434796</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84038.5760835244</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101435.430314706</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122894.062175284</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179829.919884068</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183839.910785312</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208829.005659194</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156255.369321859</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30800.9004702098</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29893.1383009412</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28366.7019699662</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34546.6689790948</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41191.4920451113</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47214.4451392733</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54169.1920257537</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63068.0118096548</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67884.1672473079</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64495.7285061199</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69295.8800575025</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79150.1907129901</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92411.3515680768</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83744.7044866217</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53499.1198545415</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368973.789780002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442478.504727879</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>422738.500516441</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353248.230464767</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>350895.204789117</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>332356.281963723</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>315653.104547513</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>372316.583403413</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394429.529831238</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>464861.8855843</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>442744.49672635</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>480614.802423602</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>563249.122579558</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>628031.481610197</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>572368.316065227</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2144518.84303576</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2000325.84482548</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1883507.59434607</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.655</t>
+          <t>1654641.4892811</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.673</t>
+          <t>1673376.93448841</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1918434.09848299</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2144925.07014545</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.517</t>
+          <t>2517372.28452516</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2919711.11699056</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3.662</t>
+          <t>3661872.78405937</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3.893</t>
+          <t>3892667.84706738</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4.256</t>
+          <t>4256039.07744085</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>5.391</t>
+          <t>5391359.27034264</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>5.867</t>
+          <t>5866589.02795295</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>6.444</t>
+          <t>6443944.52250316</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55655.6165849593</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56794.0179578744</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47524.8249543426</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49089.3400808768</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66200.9752101437</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69786.0102275696</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61183.0564373405</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54634.9591769462</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65849.3013766742</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77717.1442123389</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83111.2922161581</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89767.2387958788</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94245.8941335374</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102590.563948109</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89929.9433346103</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>504589.483482812</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553978.944982805</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>453773.755018667</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>475766.422518289</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>581621.904895131</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768135.709166928</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>757547.239355953</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>784383.469636505</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>911016.744208108</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1041198.7138722</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1235947.15915807</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>1581050.50800126</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1639628.51425112</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1706564.16407307</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1125216.36799515</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>1682864.25431933</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1564606.23911482</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1504328.37608727</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1349954.62358569</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1638744.22881875</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2170229.84925118</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>2040597.05266889</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.958</t>
+          <t>1958037.7711333</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>2252777.90277631</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>2713585.88036448</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3.294</t>
+          <t>3294184.43189756</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3.746</t>
+          <t>3746200.97747344</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.036</t>
+          <t>4036074.3810629</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5.192</t>
+          <t>5191785.01780495</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>3317260.80021357</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>633433.581035125</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>722221.453724713</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>722593.063278866</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614132.917521728</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>762319.950160125</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>999699.090399342</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>938069.569610411</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>971324.809046879</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1157280.99277276</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1420220.5352874</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1732642.18917968</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.086</t>
+          <t>2086066.45414637</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>2298359.86279047</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.809</t>
+          <t>2808750.20383326</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2103101.47417987</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10969.9618421112</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13638.906253357</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8411.09707045662</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7916.98402725137</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8050.31654674548</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7386.04679078786</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8446.72087822576</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8799.95986274465</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11294.81013838</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12624.7039232843</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16220.2903719443</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18609.3734744777</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27115.3367465309</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27241.8099199304</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15728.2166696347</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5472.09930206733</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4180.79652464516</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3650.87737839016</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4121.71461807595</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4499.33854373248</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4670.98558225453</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4291.67230119554</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3963.92282666802</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5284.52407385223</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6347.77590319532</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7101.28587839497</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7775.2620581983</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8725.61114233787</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8616.65947608999</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9734.2323509872</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3902.353342067</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4379.0071599057</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3357.68118120396</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4541.62659131203</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5322.13597620906</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5099.04571961418</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6199.30239254724</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6793.03515657863</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9040.60476065624</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15134.6829830074</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82663.8340321351</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26237.5918141741</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19459.1050123135</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19041.9772065976</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13342.8003317184</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180844.217577742</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200841.67307945</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187350.159983403</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226321.853476518</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>272134.581119901</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300237.458537826</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>336056.775878647</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>350861.67911277</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347758.496963444</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407242.267743968</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>435372.077364466</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>468533.955555492</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>500868.3914902</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538486.484267239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>434014.765954027</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4681.93584166209</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4860.02575588441</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2927.21143521836</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3997.09466950973</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6078.10457329677</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8453.47508352882</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5025.46524192674</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5051.93505074739</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5688.99508582677</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5674.1374650319</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6599.1327435635</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7334.66734360518</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7539.19277625767</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8468.09547851385</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6366.73544617646</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227228.666707043</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228301.292500606</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170863.129420623</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200094.522449801</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240879.197042029</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257093.117550747</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236361.999369892</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216993.476827925</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250747.206770595</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299498.211113088</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386886.12884166</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>449957.953302718</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>474649.331338309</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569307.698043019</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405565.875169511</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77292.7176819432</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83664.9437081016</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64761.2878936435</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76828.9195000689</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84826.2533881104</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93615.8932032266</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92179.4370272962</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103917.277163332</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116239.434003508</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140387.232430414</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>167178.587442931</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195136.266199022</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246460.710359721</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244291.641337596</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169913.728651716</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50978.9809135736</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51511.9397892857</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42979.8495422797</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44494.476668019</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56423.3518172036</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78889.6927559438</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74949.7985312264</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73095.3556076453</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83245.2232933576</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108436.255456332</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144148.348216567</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158174.434094172</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179462.079625124</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218342.633403344</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133742.3901272</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89370.873395635</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86823.8036893877</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74247.1781991965</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67883.5544648056</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66668.1443238222</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63467.3569651095</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76379.2430562187</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82517.5431334199</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85472.7822667932</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105132.935113089</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112977.786668932</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140662.948762864</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110116.009278145</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141897.709848569</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106437.054520301</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>457099.84159538</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>443205.998418397</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>338200.107915637</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326950.75687925</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259451.925517393</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283898.286286956</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>280835.214744994</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273769.401364471</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311788.41733146</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368695.299835455</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>414832.333063047</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>420383.213074325</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>520553.944513672</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>585352.145830997</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475020.5948193</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14053.4399458784</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15533.5254209022</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12140.395018452</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14563.4206705585</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15303.8975679536</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16023.1142237067</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18934.2640501264</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19419.5018047404</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25342.764170951</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41198.2848336075</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50078.1376735306</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58629.6094420734</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74115.740209461</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72124.1981808586</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66496.2782470739</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12585.4041716118</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13043.5246045312</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9678.03209106884</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11018.9319940631</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13475.0983352897</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14352.1229953205</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14637.1962473628</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16015.7248079621</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19565.0944788346</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21962.1579290301</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24944.7596965783</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28768.8605167023</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34085.4787663005</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44966.3043861509</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29417.7905715534</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93776.1843882961</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92844.4740712316</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71056.6890208239</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80636.8037655351</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101766.989379582</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126157.198647279</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117186.74626578</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107181.810206101</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127714.461669535</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137951.448899722</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150151.164603036</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169392.784831197</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184226.629910817</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171020.652754984</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115590.466225942</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181865.241803357</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201873.744866598</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232238.063351453</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235465.207955694</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242026.858431964</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>392483.301132238</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368851.584491031</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>570929.841939016</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>683514.640681727</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772248.66601244</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>888839.788390771</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1009778.81283283</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>1108091.05684499</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>937631.738993711</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>907934.783522281</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>359707.816303513</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>350707.229208491</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312827.985594148</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338564.765065738</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>421642.458005856</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564148.641834888</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>504384.532912393</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>600183.757890379</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>669949.338885286</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>819840.872775807</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870606.30575207</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>981415.917602628</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1053507.9060905</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1156718.11711127</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>760797.926939921</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>2252500.30272041</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2320109.83186801</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2099761.66633849</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2.065</t>
+          <t>2065325.80374484</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2659871.97935177</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3470334.38992469</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>3115043.85312724</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t>2976233.34926324</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>3239360.85505522</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>3918149.31851533</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4.773</t>
+          <t>4772732.6257202</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>5125310.71472844</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>5.426</t>
+          <t>5425720.03305883</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>6.229</t>
+          <t>6228557.61835978</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3699593.2631436</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36.365</t>
+          <t>36364853.0183964</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>37.261</t>
+          <t>37260504.1082445</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>39.453</t>
+          <t>39452757.0483141</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>39.585</t>
+          <t>39584623.4949045</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>40.564</t>
+          <t>40564200.9286737</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>40.351</t>
+          <t>40350931.7017737</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>39.799</t>
+          <t>39798543.9445552</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40639653.6961861</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>45.163</t>
+          <t>45163315.4635237</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>48.998</t>
+          <t>48997512.1306806</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>52.456</t>
+          <t>52455695.5736215</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>56.239</t>
+          <t>56238554.2088071</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>62.997</t>
+          <t>62996872.6551762</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>70.017</t>
+          <t>70016573.7472836</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>69.436</t>
+          <t>69436291.0563234</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
